--- a/artfynd/A 63034-2025 artfynd.xlsx
+++ b/artfynd/A 63034-2025 artfynd.xlsx
@@ -1469,7 +1469,7 @@
         <v>130180799</v>
       </c>
       <c r="B10" t="n">
-        <v>92959</v>
+        <v>92961</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 63034-2025 artfynd.xlsx
+++ b/artfynd/A 63034-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127295912</v>
       </c>
       <c r="B2" t="n">
-        <v>91780</v>
+        <v>91748</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127293400</v>
       </c>
       <c r="B3" t="n">
-        <v>57672</v>
+        <v>57657</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>127295052</v>
       </c>
       <c r="B4" t="n">
-        <v>80000</v>
+        <v>79982</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>127293769</v>
       </c>
       <c r="B5" t="n">
-        <v>57672</v>
+        <v>57657</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>127293352</v>
       </c>
       <c r="B6" t="n">
-        <v>57672</v>
+        <v>57657</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>127296759</v>
       </c>
       <c r="B7" t="n">
-        <v>80000</v>
+        <v>79982</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>127295058</v>
       </c>
       <c r="B8" t="n">
-        <v>80167</v>
+        <v>80149</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>127296834</v>
       </c>
       <c r="B9" t="n">
-        <v>79647</v>
+        <v>79629</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>130180799</v>
       </c>
       <c r="B10" t="n">
-        <v>92961</v>
+        <v>93048</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 63034-2025 artfynd.xlsx
+++ b/artfynd/A 63034-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127295912</v>
       </c>
       <c r="B2" t="n">
-        <v>91748</v>
+        <v>91780</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127293400</v>
       </c>
       <c r="B3" t="n">
-        <v>57657</v>
+        <v>57672</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>127295052</v>
       </c>
       <c r="B4" t="n">
-        <v>79982</v>
+        <v>80000</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>127293769</v>
       </c>
       <c r="B5" t="n">
-        <v>57657</v>
+        <v>57672</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>127293352</v>
       </c>
       <c r="B6" t="n">
-        <v>57657</v>
+        <v>57672</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>127296759</v>
       </c>
       <c r="B7" t="n">
-        <v>79982</v>
+        <v>80000</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>127295058</v>
       </c>
       <c r="B8" t="n">
-        <v>80149</v>
+        <v>80167</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>127296834</v>
       </c>
       <c r="B9" t="n">
-        <v>79629</v>
+        <v>79647</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>0</v>
       </c>
       <c r="AE10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG10" t="b">
         <v>0</v>

--- a/artfynd/A 63034-2025 artfynd.xlsx
+++ b/artfynd/A 63034-2025 artfynd.xlsx
@@ -1469,7 +1469,7 @@
         <v>130180799</v>
       </c>
       <c r="B10" t="n">
-        <v>93048</v>
+        <v>93051</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 63034-2025 artfynd.xlsx
+++ b/artfynd/A 63034-2025 artfynd.xlsx
@@ -1469,7 +1469,7 @@
         <v>130180799</v>
       </c>
       <c r="B10" t="n">
-        <v>93051</v>
+        <v>93077</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 63034-2025 artfynd.xlsx
+++ b/artfynd/A 63034-2025 artfynd.xlsx
@@ -1469,7 +1469,7 @@
         <v>130180799</v>
       </c>
       <c r="B10" t="n">
-        <v>93077</v>
+        <v>93078</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 63034-2025 artfynd.xlsx
+++ b/artfynd/A 63034-2025 artfynd.xlsx
@@ -1469,7 +1469,7 @@
         <v>130180799</v>
       </c>
       <c r="B10" t="n">
-        <v>93078</v>
+        <v>93079</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 63034-2025 artfynd.xlsx
+++ b/artfynd/A 63034-2025 artfynd.xlsx
@@ -1469,7 +1469,7 @@
         <v>130180799</v>
       </c>
       <c r="B10" t="n">
-        <v>93079</v>
+        <v>93081</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 63034-2025 artfynd.xlsx
+++ b/artfynd/A 63034-2025 artfynd.xlsx
@@ -1469,7 +1469,7 @@
         <v>130180799</v>
       </c>
       <c r="B10" t="n">
-        <v>93081</v>
+        <v>93085</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 63034-2025 artfynd.xlsx
+++ b/artfynd/A 63034-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>127295912</v>
       </c>
       <c r="B2" t="n">
-        <v>91780</v>
+        <v>92358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127293400</v>
+        <v>130180799</v>
       </c>
       <c r="B3" t="n">
-        <v>57672</v>
+        <v>93235</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,42 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Körttjärnet, Körttjärnet, Vrm</t>
+          <t>Körttjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>350834</v>
+        <v>350749</v>
       </c>
       <c r="R3" t="n">
-        <v>6612518</v>
+        <v>6612669</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -842,19 +837,29 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG3" t="b">
         <v>0</v>
@@ -862,12 +867,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Sofia Martinell-Funch</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Sofia Martinell-Funch</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -877,7 +882,7 @@
         <v>127295052</v>
       </c>
       <c r="B4" t="n">
-        <v>80000</v>
+        <v>80300</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -971,50 +976,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127293769</v>
+        <v>127296759</v>
       </c>
       <c r="B5" t="n">
-        <v>57672</v>
+        <v>80300</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6441</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Slanklav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Collema flaccidum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Körttjärnet, Körttjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>350738</v>
+        <v>350790</v>
       </c>
       <c r="R5" t="n">
-        <v>6612454</v>
+        <v>6612694</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1073,10 +1073,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127293352</v>
+        <v>127294348</v>
       </c>
       <c r="B6" t="n">
-        <v>57672</v>
+        <v>79946</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1084,39 +1084,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Körttjärnet, Körttjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>350807</v>
+        <v>350737</v>
       </c>
       <c r="R6" t="n">
-        <v>6612538</v>
+        <v>6612560</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1175,32 +1170,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127296759</v>
+        <v>127296834</v>
       </c>
       <c r="B7" t="n">
-        <v>80000</v>
+        <v>79946</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6441</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Slanklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Collema flaccidum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1210,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>350790</v>
+        <v>350787</v>
       </c>
       <c r="R7" t="n">
-        <v>6612694</v>
+        <v>6612666</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1275,7 +1270,7 @@
         <v>127295058</v>
       </c>
       <c r="B8" t="n">
-        <v>80167</v>
+        <v>80467</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1369,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127296834</v>
+        <v>127293352</v>
       </c>
       <c r="B9" t="n">
-        <v>79647</v>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1380,34 +1375,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Körttjärnet, Körttjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>350787</v>
+        <v>350807</v>
       </c>
       <c r="R9" t="n">
-        <v>6612666</v>
+        <v>6612538</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1466,10 +1466,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130180799</v>
+        <v>127293400</v>
       </c>
       <c r="B10" t="n">
-        <v>93085</v>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1477,37 +1477,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5966</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Körttjärnet, Vrm</t>
+          <t>Körttjärnet, Körttjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>350749</v>
+        <v>350834</v>
       </c>
       <c r="R10" t="n">
-        <v>6612669</v>
+        <v>6612518</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1531,29 +1536,19 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>10:19</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>10:19</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="b">
         <v>0</v>
@@ -1561,15 +1556,117 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Sofia Martinell-Funch</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Sofia Martinell-Funch</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>127293769</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Körttjärnet, Körttjärnet, Vrm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>350738</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6612454</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Älgå</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
